--- a/result.xlsx
+++ b/result.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI25"/>
+  <dimension ref="A1:AK26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -458,6 +458,8 @@
     <col width="20" customWidth="1" min="33" max="33"/>
     <col width="15" customWidth="1" min="34" max="34"/>
     <col width="71" customWidth="1" min="35" max="35"/>
+    <col width="35" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -636,6 +638,16 @@
           <t>challenge</t>
         </is>
       </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>query</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>course</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2254,12 +2266,6 @@
           <t>screenshots/SABURI_TC_1_saburi.png</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>noor.mohammed@terralogic.com</t>
@@ -2300,21 +2306,93 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ACADEMY_TC_25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>academy</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://terralogic.academy/</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-04-08 11:42:50</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>screenshots/ACADEMY_TC_1_academy.png</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>9876543210</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Noor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>I want to enroll in UI/UX course</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/result.xlsx
+++ b/result.xlsx
@@ -38,14 +38,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
-        <bgColor rgb="00FF0000"/>
+        <fgColor rgb="0000FF00"/>
+        <bgColor rgb="0000FF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000FF00"/>
-        <bgColor rgb="0000FF00"/>
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -431,10 +431,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH18"/>
+  <dimension ref="A1:AH13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="51" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -445,13 +445,13 @@
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="31" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
     <col width="23" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
@@ -513,52 +513,52 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>offer_code</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>full_name</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>type</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
@@ -645,62 +645,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ENQUIRY_TC_1</t>
+          <t>GENERAL_TC_1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://lollypop.terralogic.com/project-enquiry/</t>
+          <t>https://lollypop.design/general-enquiry/</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-08 12:25:39</t>
+          <t>2026-04-08 13:05:31</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>screenshots/ENQUIRY_TC_1_enquiry.png</t>
+          <t>screenshots/GENERAL_TC_1_general.png</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>I need a UI/UX design for my project</t>
+          <t xml:space="preserve"> Generalenquiry</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ProjectEnquiry</t>
+          <t>GeneralEnquiry</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>noor.mohammed@terralogic</t>
+          <t>noor.mohammed@terralogic.com</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>9876543210</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>FREE100 enquiry</t>
         </is>
       </c>
     </row>
@@ -722,10 +717,10 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-08 12:27:36</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+          <t>2026-04-08 13:05:45</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -740,6 +735,11 @@
           <t xml:space="preserve"> Generalenquiry</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>GeneralEnquiry</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>noor.mohammed@terralogic.com</t>
@@ -748,18 +748,13 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>invalid dta inputs</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>GeneralEnquiry</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SABURI_TC_3</t>
+          <t>SABURI_TC_1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -774,10 +769,10 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-08 12:29:52</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+          <t>2026-04-08 13:06:48</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -792,11 +787,6 @@
           <t>screenshots/SABURI_TC_1_saburi.png</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>noor.mohammed@terralogic.com</t>
@@ -807,27 +797,32 @@
           <t>9876543210</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>SaburiName</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ABC Pvt Ltd</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ABC Pvt Ltd</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Co-working</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Co-working</t>
+          <t>Need office space</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
-        <is>
-          <t>Need office space</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
@@ -836,7 +831,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SABURI_TC_4</t>
+          <t>SABURI_TC_2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -851,10 +846,10 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-08 12:30:53</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+          <t>2026-04-08 13:07:15</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -866,45 +861,45 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>screenshots/SABURI_TC_1_saburi.png</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+          <t>screenshots/SABURI_TC_2_saburi.png</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>noor.mohammed@terralogic</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>9876543210</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>SaburiName</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>noor.mohammed@terralogic</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>9876543210</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ABC Pvt Ltd</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ABC Pvt Ltd</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Co-working</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Co-working</t>
+          <t>Need office space</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
-        <is>
-          <t>Need office space</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
@@ -913,42 +908,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SHANKARA_TC_5</t>
+          <t>ENQUIRY_TC_1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>shankara</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://shankarbaba.org/contact-us/</t>
+          <t>https://lollypop.terralogic.com/project-enquiry/</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-08 12:32:24</t>
+          <t>2026-04-08 13:08:22</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>screenshots/shankara.png</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>shankaraName</t>
+          <t>screenshots/ENQUIRY_TC_1_enquiry.png</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>I need a UI/UX design for my project</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -956,72 +951,66 @@
           <t>noor.mohammed@terralogic.com</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Test message</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>invalid input data</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>9876543210</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ProjectEnquiry</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>FREE100 enquiry</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GENERAL_TC_6</t>
+          <t>ENQUIRY_TC_2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://lollypop.design/general-enquiry/</t>
+          <t>https://lollypop.terralogic.com/project-enquiry/</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-08 12:34:07</t>
+          <t>2026-04-08 13:08:53</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>screenshots/GENERAL_TC_1_general.png</t>
+          <t>screenshots/ENQUIRY_TC_2_enquiry.png</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Generalenquiry</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>I need a UI/UX design for my project</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>noor.mohammed@terralogic.com</t>
+          <t>noor.mohammed@terralogic</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1029,124 +1018,118 @@
           <t>9876543210</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>GeneralEnquiry</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ProjectEnquiry</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>FREE100 enquiry</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GENERAL_TC_7</t>
+          <t>SHANKARA_TC_1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>shankara</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://lollypop.design/general-enquiry/</t>
+          <t>https://shankarbaba.org/contact-us/</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-08 12:34:22</t>
+          <t>2026-04-08 13:09:42</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Generalenquiry</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>screenshots/shankara.png</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>noor.mohammed@terralogic.com</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>invalid dta inputs</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>GeneralEnquiry</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>shankaraName</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Test message</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>9876543210</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SABURI_TC_8</t>
+          <t>SHANKARA_TC_2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>saburi</t>
+          <t>shankara</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://saburi.works/contact/</t>
+          <t>https://shankarbaba.org/contact-us/</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-08 12:34:50</t>
+          <t>2026-04-08 13:10:09</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>screenshots/SABURI_TC_1_saburi.png</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>SaburiName</t>
+          <t>screenshots/shankara.png</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1154,169 +1137,183 @@
           <t>noor.mohammed@terralogic.com</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>9876543210</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>ABC Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>shankaraName</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Test message</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>invalid input data</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Co-working</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Need office space</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SABURI_TC_9</t>
+          <t>MRCEO_TC_1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>saburi</t>
+          <t>mrceo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://saburi.works/contact/</t>
+          <t>https://mrceo.biz/contact-us/#investment</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-08 12:35:18</t>
+          <t>2026-04-08 13:12:12</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>screenshots/SABURI_TC_2_saburi.png</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>SaburiName</t>
+          <t>screenshots/MRCEO_TC_1_mrceo.png</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>noor.mohammed@terralogic</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+          <t>noor.mohammed@terralogic.com</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>9876543210</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>ABC Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Co-working</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Need office space</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>TC001</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>investment</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>MrCEONamefiled</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/rajeshkumar</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>TechVision Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>info@techvision.com</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>https://techvision.com</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>https://instagram.com/techvision</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Technology / SaaS</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Growth Stage</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>We need funding to expand our SaaS product to international markets.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ENQUIRY_TC_10</t>
+          <t>MRCEO_TC_2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>mrceo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://lollypop.terralogic.com/project-enquiry/</t>
+          <t>https://mrceo.biz/contact-us/#investment</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-08 12:35:50</t>
+          <t>2026-04-08 13:13:49</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>screenshots/ENQUIRY_TC_1_enquiry.png</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>I need a UI/UX design for my project</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ProjectEnquiry</t>
+          <t>screenshots/MRCEO_TC_2_mrceo.png</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1324,75 +1321,123 @@
           <t>noor.mohammed@terralogic.com</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>9876543210</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>FREE100 enquiry</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>incorrect input data</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>TC001</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>investment</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>MrCEONamefiled</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/rajeshkumar</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>TechVision Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>info@techvision.com</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>https://techvision.com</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>https://instagram.com/techvision</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Technology / SaaS</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Growth Stage</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>We need funding to expand our SaaS product to international markets.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ENQUIRY_TC_11</t>
+          <t>ACADEMY_TC_1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>academy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://lollypop.terralogic.com/project-enquiry/</t>
+          <t>https://terralogic.academy/</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-08 12:36:22</t>
+          <t>2026-04-08 13:14:28</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>screenshots/ENQUIRY_TC_2_enquiry.png</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>I need a UI/UX design for my project</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>ProjectEnquiry</t>
-        </is>
-      </c>
+          <t>screenshots/ACADEMY_TC_1_academy.png</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>noor.mohammed@terralogic</t>
+          <t>test@gmail.com</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1402,7 +1447,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>FREE100 enquiry</t>
+          <t>Noor</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1413,581 +1458,116 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>I want to enroll in UI/UX course</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SHANKARA_TC_12</t>
+          <t>ACADEMY_TC_2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>shankara</t>
+          <t>academy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://shankarbaba.org/contact-us/</t>
+          <t>https://terralogic.academy/</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-08 12:36:51</t>
+          <t>2026-04-08 13:15:00</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>screenshots/shankara.png</t>
+          <t>screenshots/ACADEMY_TC_2_academy_fail.png</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>shankaraName</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>noor.mohammed@terralogic.com</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>9876543210</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Noor</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Test message</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>9876543210</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SHANKARA_TC_13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>shankara</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://shankarbaba.org/contact-us/</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-04-08 12:37:18</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>screenshots/shankara.png</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>shankaraName</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>noor.mohammed@terralogic.com</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Test message</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>invalid input data</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MRCEO_TC_14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>mrceo</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://mrceo.biz/contact-us/#investment</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-04-08 12:38:58</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>screenshots/MRCEO_TC_1_mrceo.png</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>noor.mohammed@terralogic.com</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>valid</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>9876543210</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>TC001</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>investment</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>MrCEONamefiled</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/rajeshkumar</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>TechVision Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>info@techvision.com</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>https://techvision.com</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>https://instagram.com/techvision</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>Technology / SaaS</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>Growth Stage</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>We need funding to expand our SaaS product to international markets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MRCEO_TC_15</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>mrceo</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://mrceo.biz/contact-us/#investment</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-04-08 12:40:35</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>screenshots/MRCEO_TC_2_mrceo.png</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>noor.mohammed@terralogic.com</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>valid</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>incorrect input data</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>TC001</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>investment</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>MrCEONamefiled</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/rajeshkumar</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>TechVision Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>info@techvision.com</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>https://techvision.com</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>https://instagram.com/techvision</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>Technology / SaaS</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>Growth Stage</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>We need funding to expand our SaaS product to international markets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ACADEMY_TC_16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>academy</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://terralogic.academy/</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-04-08 12:40:45</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>screenshots/ACADEMY_TC_1_academy.png</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Noor</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>test@gmail.com</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>9876543210</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr">
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr">
         <is>
           <t>I want to enroll in UI/UX course</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ACADEMY_TC_17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>academy</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://terralogic.academy/</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-04-08 12:41:18</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>screenshots/ACADEMY_TC_2_academy_fail.png</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Noor</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>test@gmail.com</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>9876543210</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>I want to enroll in UI/UX course</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AH13" t="inlineStr">
         <is>
           <t>UI/UX</t>
         </is>
